--- a/AAII_Financials/Yearly/OOMA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OOMA_YR_FIN.xlsx
@@ -784,7 +784,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>106300</v>
+        <v>106400</v>
       </c>
       <c r="E9" s="3">
         <v>100800</v>
@@ -835,13 +835,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>167300</v>
+        <v>167200</v>
       </c>
       <c r="E10" s="3">
         <v>156000</v>
       </c>
       <c r="F10" s="3">
-        <v>147300</v>
+        <v>147200</v>
       </c>
       <c r="G10" s="3">
         <v>137700</v>
